--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T09:37:24+00:00</t>
+    <t>2026-01-28T12:34:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T12:34:00+00:00</t>
+    <t>2026-01-30T08:45:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Title</t>
   </si>
   <si>
+    <t>AT Messaging Event Type</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -51,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T08:45:51+00:00</t>
+    <t>2026-02-02T14:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Austria</t>
+    <t/>
   </si>
   <si>
     <t>Description</t>
@@ -336,132 +342,138 @@
       <c r="A5" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -476,58 +488,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:50:43+00:00</t>
+    <t>2026-03-18T15:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:56:08+00:00</t>
+    <t>2026-04-09T09:35:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:35:35+00:00</t>
+    <t>2026-04-09T10:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T10:04:08+00:00</t>
+    <t>2026-04-09T11:10:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:10:35+00:00</t>
+    <t>2026-04-09T11:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/CodeSystem-at-messaging-event-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:58:42+00:00</t>
+    <t>2026-05-06T12:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Level</t>
@@ -166,6 +166,15 @@
   </si>
   <si>
     <t>The transfer of a status update as a response to another message is the main purpose of the message.</t>
+  </si>
+  <si>
+    <t>questionnaireResponse</t>
+  </si>
+  <si>
+    <t>A questionnare response to a predefined questionnaire is sent.</t>
+  </si>
+  <si>
+    <t>The transfer of an ad-hoc questionnaire response is the main purpose of the message.</t>
   </si>
 </sst>
 </file>
@@ -483,7 +492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -542,6 +551,20 @@
         <v>50</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
